--- a/astro-site/public/dl/plan-negocio-panaderia/checklist-apertura-panaderia.xlsx
+++ b/astro-site/public/dl/plan-negocio-panaderia/checklist-apertura-panaderia.xlsx
@@ -14,7 +14,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F5" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F6" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'F1'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'F2'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'F3'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'F4'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'F5'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'F6'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -22,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,6 +58,11 @@
     <font>
       <name val="Calibri"/>
       <color rgb="001A1A1A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -91,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -106,10 +118,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -469,9 +492,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -495,6 +518,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -748,12 +772,52 @@
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C15">
+        <f>COUNTIF(A5:A13,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E15">
+        <f>COUNTIF(B5:B13,"?*")</f>
+        <v>9.0</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <conditionalFormatting sqref="A5:E13">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$A5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,☐,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -761,9 +825,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -787,6 +851,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1028,13 +1093,53 @@
         <is>
           <t>Potencia alta: hornos + camara frio</t>
         </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C14">
+        <f>COUNTIF(A5:A12,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E14">
+        <f>COUNTIF(B5:B12,"?*")</f>
+        <v>8.0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <conditionalFormatting sqref="A5:E12">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$A5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,☐,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1042,7 +1147,1084 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CHECKLIST APERTURA — PANADERIA / OBRADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>FASE 3: EQUIPAMIENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>TRAMITE</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>RESPONSABLE</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>PLAZO</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>NOTAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Horno de pisos o rotativo</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>4-8sem</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Pisos=artesanal, rotativo=volumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Amasadora espiral 25-50kg</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>2-3sem</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Capacidad segun produccion diaria</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Divisora + boleadora</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>2-3sem</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Produccion en serie</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Camara fermentacion controlada</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>3-4sem</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Fermentacion lenta nocturna programable</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Camara frigorifica + congelador</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>2sem</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Almacen MP + masa congelada</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Laminadora (si bolleria)</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>2-3sem</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Croissants, hojaldre</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Mesa inox + estanterias obrador</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>1-2sem</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Superficie trabajo suficiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Salida humos + campana + extractor</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Instalador</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>1-2sem</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Obligatoria</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Vitrina expositor</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>2sem</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Pan y bolleria del dia</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Mostrador tienda + caja</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Carpintero</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>2-3sem</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>TPV + balanza</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>1sem</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Bandejas, moldes, utensilios</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Proveedor</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>1sem</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C18">
+        <f>COUNTIF(A5:A16,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E18">
+        <f>COUNTIF(B5:B16,"?*")</f>
+        <v>12.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A5:E16">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$A5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,☐,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CHECKLIST APERTURA — PANADERIA / OBRADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>FASE 4: PERSONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>TRAMITE</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>RESPONSABLE</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>PLAZO</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>NOTAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Organigrama y turnos</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>1sem</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Turno madrugada 4-5AM critico</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Buscar maestro panadero</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>2-4sem</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Experiencia masa madre y fermentacion lenta</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Contratos</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Gestor</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Convenio hosteleria/alimentacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Alta SS trabajadores</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Gestor</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>Antes alta</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Manipulador alimentos</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>PRL (hornos, cargas, madrugada)</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>1-2sem</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Riesgos especificos: quemaduras, harina en aire</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Formacion masa madre y fermentacion</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Maestro</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>1-2sem</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Estandarizar: tiempos, temperaturas, hidratacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Formacion APPCC panaderia</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Alergenos gluten critico, trazabilidad harinas</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C14">
+        <f>COUNTIF(A5:A12,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E14">
+        <f>COUNTIF(B5:B12,"?*")</f>
+        <v>8.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A5:E12">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$A5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,☐,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CHECKLIST APERTURA — PANADERIA / OBRADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>FASE 5: MARKETING</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>TRAMITE</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>RESPONSABLE</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>PLAZO</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>NOTAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Identidad visual</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Disenador</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>2-3sem</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Estilo artesanal, rustico o moderno</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Google My Business</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Categoria: Panaderia. Fotos pan recien hecho</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Fotos masa madre, proceso, hornada fresca</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Web basica</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Dev</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>1-2sem</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Con horario, carta, pedidos mayorista</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Fotos profesionales</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Fotografo</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Pan saliendo horno, miga, corteza, obrador</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Acuerdos restaurantes/hoteles</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>2-4sem</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Canal mayorista: ingresos recurrentes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Rotulacion</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Rotulista</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>1sem</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Inauguracion</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>1d</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Degustacion pan + cafe gratis</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Tarjeta fidelizacion</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>1sem</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>10a barra gratis</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C15">
+        <f>COUNTIF(A5:A13,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E15">
+        <f>COUNTIF(B5:B13,"?*")</f>
+        <v>9.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A5:E13">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$A5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,☐,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1064,10 +2246,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FASE 3: EQUIPAMIENTO</t>
-        </is>
-      </c>
-    </row>
+          <t>FASE 6: 90 DIAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1103,22 +2286,22 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Horno de pisos o rotativo</t>
+          <t>Control produccion diaria (kg)</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Proveedor</t>
+          <t>Maestro</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>4-8sem</t>
+          <t>Diario</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Pisos=artesanal, rotativo=volumen</t>
+          <t>Ajustar produccion a demanda real</t>
         </is>
       </c>
     </row>
@@ -1130,22 +2313,22 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Amasadora espiral 25-50kg</t>
+          <t>Control merma pan no vendido</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Proveedor</t>
+          <t>Titular</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>2-3sem</t>
+          <t>Diario</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Capacidad segun produccion diaria</t>
+          <t>Objetivo: &lt;8% merma</t>
         </is>
       </c>
     </row>
@@ -1157,22 +2340,22 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Divisora + boleadora</t>
+          <t>Food cost semanal</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Proveedor</t>
+          <t>Titular</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>2-3sem</t>
+          <t>Semanal</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Produccion en serie</t>
+          <t>Controlar harina, mantequilla, chocolate</t>
         </is>
       </c>
     </row>
@@ -1184,22 +2367,22 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Camara fermentacion controlada</t>
+          <t>Ajustar carta</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Proveedor</t>
+          <t>Titular</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>3-4sem</t>
+          <t>Mes 1</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Fermentacion lenta nocturna programable</t>
+          <t>Potenciar lo que mas se vende</t>
         </is>
       </c>
     </row>
@@ -1211,22 +2394,22 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Camara frigorifica + congelador</t>
+          <t>Optimizar horario produccion</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Proveedor</t>
+          <t>Maestro</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>2sem</t>
+          <t>Mes 1</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Almacen MP + masa congelada</t>
+          <t>Tener pan fresco a las 7:30 y a las 17:00</t>
         </is>
       </c>
     </row>
@@ -1238,22 +2421,22 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Laminadora (si bolleria)</t>
+          <t>Resenas Google</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Proveedor</t>
+          <t>Titular</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>2-3sem</t>
+          <t>Mes 1-3</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Croissants, hojaldre</t>
+          <t>Pedir, responder todas</t>
         </is>
       </c>
     </row>
@@ -1265,22 +2448,22 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Mesa inox + estanterias obrador</t>
+          <t>Evaluar canal mayorista</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Proveedor</t>
+          <t>Titular</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>1-2sem</t>
+          <t>Mes 2</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Superficie trabajo suficiente</t>
+          <t>Restaurantes y hoteles = volumen estable</t>
         </is>
       </c>
     </row>
@@ -1292,22 +2475,22 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Salida humos + campana + extractor</t>
+          <t>Renegociar proveedores harinas</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Instalador</t>
+          <t>Titular</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>1-2sem</t>
+          <t>Mes 2</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Obligatoria</t>
+          <t>Con volumen real</t>
         </is>
       </c>
     </row>
@@ -1319,22 +2502,22 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Vitrina expositor</t>
+          <t>Cierre trimestral</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Proveedor</t>
+          <t>Gestor</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>2sem</t>
+          <t>Mes 3</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Pan y bolleria del dia</t>
+          <t>P&amp;L real vs plan</t>
         </is>
       </c>
     </row>
@@ -1346,983 +2529,69 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Mostrador tienda + caja</t>
+          <t>Evaluar 2o turno produccion</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Carpintero</t>
+          <t>Titular</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>2-3sem</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>TPV + balanza</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Proveedor</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>1sem</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr"/>
-    </row>
+          <t>Mes 3</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Si demanda crece: turno tarde para bolleria</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Bandejas, moldes, utensilios</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Proveedor</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>1sem</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr"/>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C16">
+        <f>COUNTIF(A5:A14,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E16">
+        <f>COUNTIF(B5:B14,"?*")</f>
+        <v>10.0</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>CHECKLIST APERTURA — PANADERIA / OBRADOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>FASE 4: PERSONAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>TRAMITE</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>RESPONSABLE</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>PLAZO</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>NOTAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Organigrama y turnos</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>1sem</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>Turno madrugada 4-5AM critico</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Buscar maestro panadero</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>2-4sem</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>Experiencia masa madre y fermentacion lenta</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Contratos</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Gestor</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Convenio hosteleria/alimentacion</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Alta SS trabajadores</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Gestor</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>Antes alta</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Manipulador alimentos</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>PRL (hornos, cargas, madrugada)</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>SPA</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>1-2sem</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>Riesgos especificos: quemaduras, harina en aire</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Formacion masa madre y fermentacion</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Maestro</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>1-2sem</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Estandarizar: tiempos, temperaturas, hidratacion</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Formacion APPCC panaderia</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Alergenos gluten critico, trazabilidad harinas</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>CHECKLIST APERTURA — PANADERIA / OBRADOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>FASE 5: MARKETING</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>TRAMITE</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>RESPONSABLE</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>PLAZO</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>NOTAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Identidad visual</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Disenador</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>2-3sem</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>Estilo artesanal, rustico o moderno</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Google My Business</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>Categoria: Panaderia. Fotos pan recien hecho</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Fotos masa madre, proceso, hornada fresca</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Web basica</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Dev</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>1-2sem</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>Con horario, carta, pedidos mayorista</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Fotos profesionales</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Fotografo</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Pan saliendo horno, miga, corteza, obrador</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Acuerdos restaurantes/hoteles</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>2-4sem</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>Canal mayorista: ingresos recurrentes</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Rotulacion</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Rotulista</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>1sem</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Inauguracion</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>1d</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Degustacion pan + cafe gratis</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Tarjeta fidelizacion</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>1sem</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>10a barra gratis</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>CHECKLIST APERTURA — PANADERIA / OBRADOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>FASE 6: 90 DIAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>TRAMITE</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>RESPONSABLE</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>PLAZO</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>NOTAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Control produccion diaria (kg)</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Maestro</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Diario</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>Ajustar produccion a demanda real</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Control merma pan no vendido</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>Diario</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>Objetivo: &lt;8% merma</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Food cost semanal</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Semanal</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Controlar harina, mantequilla, chocolate</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Ajustar carta</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>Mes 1</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>Potenciar lo que mas se vende</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Optimizar horario produccion</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Maestro</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Mes 1</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Tener pan fresco a las 7:30 y a las 17:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Resenas Google</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>Mes 1-3</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>Pedir, responder todas</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Evaluar canal mayorista</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Mes 2</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Restaurantes y hoteles = volumen estable</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Renegociar proveedores harinas</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>Mes 2</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>Con volumen real</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Cierre trimestral</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Gestor</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Mes 3</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>P&amp;L real vs plan</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Evaluar 2o turno produccion</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Titular</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>Mes 3</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>Si demanda crece: turno tarde para bolleria</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <conditionalFormatting sqref="A5:E14">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$A5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,☐,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/plan-negocio-panaderia/checklist-apertura-panaderia.xlsx
+++ b/astro-site/public/dl/plan-negocio-panaderia/checklist-apertura-panaderia.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F4" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F5" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="F6" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'F1'!$4:$4</definedName>
@@ -29,7 +30,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,8 +66,13 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -83,6 +89,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F5F0E8"/>
         <bgColor rgb="00F5F0E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -103,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -119,16 +130,50 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00C8E6C9"/>
           <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -494,7 +539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -504,17 +549,17 @@
     <col width="40" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>CHECKLIST APERTURA — PANADERIA / OBRADOR</t>
+    <row r="1" ht="75" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>CHECKLIST APERTURA — PANADERÍA / OBRADOR</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FASE 1: CONSTITUCION</t>
+          <t>FASE 1: CONSTITUCIÓN</t>
         </is>
       </c>
     </row>
@@ -527,7 +572,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>TRAMITE</t>
+          <t>TRÁMITE</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -547,14 +592,14 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Forma juridica (SL)</t>
+          <t>Forma jurídica (SL)</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -569,19 +614,19 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Capital 1 EUR</t>
+          <t>Capital 1 €</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Constitucion SL</t>
+          <t>Constitución SL</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -597,7 +642,7 @@
       <c r="E6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -619,12 +664,12 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>IAE 471.1 pan y bolleria</t>
+          <t>Epígrafe IAE: 644.1 (comercio al por menor de pan, pastelería, confitería y similares) para la venta en tienda; si el canal mayorista pesa de verdad en tu facturación, consulta con tu gestor si corresponde además el 419.1 (industrias del pan, la bollería y la pastelería) — la elección la valida tu gestor</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -646,12 +691,12 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Tarifa plana</t>
+          <t>Cuota según la base mínima del tramo que te corresponda. Consulta el importe del ejercicio en curso y verifica con tu gestoría si te aplica la cuota reducida de inicio de actividad</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -674,7 +719,7 @@
       <c r="E9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -697,14 +742,14 @@
       <c r="E10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>RGSEAA obrador</t>
+          <t>Inscripción en el Registro Sanitario de tu Comunidad Autónoma (declaración responsable de inicio de actividad alimentaria)</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -719,12 +764,12 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Obligatorio elaboracion pan</t>
+          <t>El Registro General Sanitario estatal (RGSEAA) NO aplica al minorista que sirve al consumidor final (art. 2.2 del RD 191/2011): el que te toca por la venta en tienda es el autonómico. PERO si el canal mayorista (venta a otros negocios: restaurantes, hoteles) crece más allá de un reparto puntual, consulta con tu gestoría si tu volumen y forma de venta te obligan además a la inscripción en el RGSEAA — la exención del minorista puro no cubre automáticamente al mayorista</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -746,12 +791,12 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Min 300K EUR</t>
+          <t>Mínimo 300.000 € de cobertura</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -773,38 +818,98 @@
       </c>
       <c r="E13" s="5" t="inlineStr"/>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="B15" s="8" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Registro de actividades de tratamiento de datos personales</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>Antes de abrir</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>Art. 30 del RGPD y art. 31 de la LOPDGDD: lo pide la AEPD en la primera inspección. Incluye clientes, personal y proveedores (harineras, distribuidores)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="105" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>Adaptar el TPV y la facturación al sistema Veri*factu / factura electrónica</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Gestor</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>Antes de abrir</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>El RD 1007/2023 y su calendario escalonado obligan a que el software de facturación sea verificable. Consulta la fecha que te aplica antes de comprar el TPV + balanza que presupuesta la hoja de Inversión — y ten en cuenta el canal mayorista, que factura a otras empresas</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C15">
-        <f>COUNTIF(A5:A13,"✓")</f>
+      <c r="C17" s="14">
+        <f>COUNTIF(A5:A15,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E15">
-        <f>COUNTIF(B5:B13,"?*")</f>
-        <v>9.0</v>
+      <c r="E17" s="14">
+        <f>COUNTIF(B5:B15,"?*")-COUNTIF(A5:A15,"N/A")</f>
+        <v>11.0</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:E13">
+  <conditionalFormatting sqref="A5:E15">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$A5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A5:A15">
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="1" stopIfTrue="1" text="✓">
+      <formula>NOT(ISERROR(SEARCH("✓",A5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
       <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -827,7 +932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -837,10 +942,10 @@
     <col width="40" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>CHECKLIST APERTURA — PANADERIA / OBRADOR</t>
+    <row r="1" ht="75" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>CHECKLIST APERTURA — PANADERÍA / OBRADOR</t>
         </is>
       </c>
     </row>
@@ -860,7 +965,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>TRAMITE</t>
+          <t>TRÁMITE</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -880,14 +985,14 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Busqueda local (zona+obrador)</t>
+          <t>Búsqueda local (zona+obrador)</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -902,12 +1007,12 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Min 80m2: obrador+tienda+almacen</t>
+          <t>Mínimo 80 m²: obrador + tienda + almacén</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -934,14 +1039,14 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Informe urbanistico</t>
+          <t>Informe urbanístico</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -961,7 +1066,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -988,14 +1093,14 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Proyecto tecnico (salida humos, potencia)</t>
+          <t>Proyecto técnico (salida humos, potencia)</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1010,12 +1115,12 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Critico: hornos necesitan mucha potencia</t>
+          <t>Crítico: hornos necesitan mucha potencia</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1042,7 +1147,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1064,19 +1169,19 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Incendio critico por hornos</t>
+          <t>Incendio crítico por hornos</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Contrato suministro electrico (30-40 kW)</t>
+          <t>Contrato suministro eléctrico (30-40 kW)</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -1091,42 +1196,156 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Potencia alta: hornos + camara frio</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="B14" s="8" t="inlineStr">
+          <t>Potencia alta: hornos + cámara frío</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Hojas de reclamaciones oficiales y su cartel anunciador</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>1 día</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>El modelo y el texto del cartel los aprueba tu Comunidad Autónoma</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Contrato con gestor autorizado de residuos</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>2 semanas</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>Se comprueba en la inspección. Cartón y orgánico (masa y restos de obrador); este plan no fríe, así que no hay aceite usado de fritura que gestionar</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Contrato de desinsectación, desratización y desinfección (DDD)</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>1 semana</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>Empresa inscrita en el ROESB; el certificado forma parte del plan APPCC. La harina almacenada es un foco habitual de plaga: no lo dejes para después de abrir</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="45" customHeight="1">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Cartel y contrato de videovigilancia con la empresa de seguridad</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>Con la obra</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="inlineStr">
+        <is>
+          <t>Cartel homologado en zona visible, contrato de encargado de tratamiento y plazo máximo de conservación de 30 días</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C14">
-        <f>COUNTIF(A5:A12,"✓")</f>
+      <c r="C18" s="14">
+        <f>COUNTIF(A5:A16,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E14">
-        <f>COUNTIF(B5:B12,"?*")</f>
-        <v>8.0</v>
+      <c r="E18" s="14">
+        <f>COUNTIF(B5:B16,"?*")-COUNTIF(A5:A16,"N/A")</f>
+        <v>12.0</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:E12">
+  <conditionalFormatting sqref="A5:E16">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$A5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A5:A16">
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="1" stopIfTrue="1" text="✓">
+      <formula>NOT(ISERROR(SEARCH("✓",A5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
       <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1159,10 +1378,10 @@
     <col width="40" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>CHECKLIST APERTURA — PANADERIA / OBRADOR</t>
+    <row r="1" ht="75" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>CHECKLIST APERTURA — PANADERÍA / OBRADOR</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1401,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>TRAMITE</t>
+          <t>TRÁMITE</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1202,7 +1421,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1229,7 +1448,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1251,12 +1470,12 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Capacidad segun produccion diaria</t>
+          <t>Capacidad según producción diaria</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1278,19 +1497,19 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Produccion en serie</t>
+          <t>Producción en serie</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Camara fermentacion controlada</t>
+          <t>Cámara fermentación controlada</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -1305,19 +1524,19 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Fermentacion lenta nocturna programable</t>
+          <t>Fermentación lenta nocturna programable</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Camara frigorifica + congelador</t>
+          <t>Cámara frigorífica + congelador</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1332,19 +1551,19 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Almacen MP + masa congelada</t>
+          <t>Almacén MP + masa congelada</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Laminadora (si bolleria)</t>
+          <t>Laminadora (si bollería)</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -1364,14 +1583,14 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Mesa inox + estanterias obrador</t>
+          <t>Mesa inox + estanterías obrador</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -1391,7 +1610,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1418,7 +1637,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1440,12 +1659,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Pan y bolleria del dia</t>
+          <t>Pan y bollería del día</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1468,7 +1687,7 @@
       <c r="E14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1491,7 +1710,7 @@
       <c r="E15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1520,7 +1739,7 @@
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C18">
+      <c r="C18" s="14">
         <f>COUNTIF(A5:A16,"✓")</f>
         <v>0.0</v>
       </c>
@@ -1529,12 +1748,13 @@
           <t>de</t>
         </is>
       </c>
-      <c r="E18">
-        <f>COUNTIF(B5:B16,"?*")</f>
+      <c r="E18" s="14">
+        <f>COUNTIF(B5:B16,"?*")-COUNTIF(A5:A16,"N/A")</f>
         <v>12.0</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
@@ -1543,8 +1763,13 @@
       <formula>$A5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A5:A16">
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="1" stopIfTrue="1" text="✓">
+      <formula>NOT(ISERROR(SEARCH("✓",A5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
       <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1567,7 +1792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1577,10 +1802,10 @@
     <col width="40" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>CHECKLIST APERTURA — PANADERIA / OBRADOR</t>
+    <row r="1" ht="75" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>CHECKLIST APERTURA — PANADERÍA / OBRADOR</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1825,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>TRAMITE</t>
+          <t>TRÁMITE</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1620,7 +1845,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1642,12 +1867,12 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Turno madrugada 4-5AM critico</t>
+          <t>Turno madrugada 4-5AM crítico</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1669,12 +1894,12 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Experiencia masa madre y fermentacion lenta</t>
+          <t>Experiencia masa madre y fermentación lenta</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1696,12 +1921,12 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Convenio hosteleria/alimentacion</t>
+          <t>Convenio hostelería/alimentación</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1724,19 +1949,19 @@
       <c r="E8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Manipulador alimentos</t>
+          <t>Formación en higiene alimentaria de todo el equipo (el «carnet» está DEROGADO, RD 109/2010: la formación la acredita la EMPRESA y se documenta en el plan APPCC)</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>Titular</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -1747,19 +1972,19 @@
       <c r="E9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>PRL (hornos, cargas, madrugada)</t>
+          <t>PRL (hornos, cargas, madrugada) — el plan de prevención es obligatorio; el proveedor externo, no: con menos de 25 trabajadores y un solo centro el titular puede asumir la actividad preventiva (art. 30.5 de la Ley 31/1995 y art. 11 del RD 39/1997)</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>Titular o servicio ajeno</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -1769,19 +1994,19 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Riesgos especificos: quemaduras, harina en aire</t>
+          <t>Riesgos específicos: quemaduras, harina en aire</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Formacion masa madre y fermentacion</t>
+          <t>Formación masa madre y fermentación</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -1796,19 +2021,19 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Estandarizar: tiempos, temperaturas, hidratacion</t>
+          <t>Estandarizar: tiempos, temperaturas, hidratación</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Formacion APPCC panaderia</t>
+          <t>Formación APPCC panadería</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -1823,42 +2048,102 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Alergenos gluten critico, trazabilidad harinas</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="B14" s="8" t="inlineStr">
+          <t>Alérgenos gluten crítico, trazabilidad harinas</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Registro horario diario de la jornada de todo el equipo</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>Gestor</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>Desde el primer contrato</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>Art. 34.9 del Estatuto de los Trabajadores; se conserva cuatro años. Especialmente relevante con el turno de madrugada del maestro panadero</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Informar al equipo del registro horario y del tratamiento de sus datos</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>Gestor</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>Desde el primer contrato</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>La cláusula informativa se entrega con el contrato; el fichaje es un tratamiento de datos, no sólo una obligación laboral</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C14">
-        <f>COUNTIF(A5:A12,"✓")</f>
+      <c r="C16" s="14">
+        <f>COUNTIF(A5:A14,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E14">
-        <f>COUNTIF(B5:B12,"?*")</f>
-        <v>8.0</v>
+      <c r="E16" s="14">
+        <f>COUNTIF(B5:B14,"?*")-COUNTIF(A5:A14,"N/A")</f>
+        <v>10.0</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:E12">
+  <conditionalFormatting sqref="A5:E14">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$A5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A5:A14">
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="1" stopIfTrue="1" text="✓">
+      <formula>NOT(ISERROR(SEARCH("✓",A5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
       <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1881,7 +2166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1891,10 +2176,10 @@
     <col width="40" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>CHECKLIST APERTURA — PANADERIA / OBRADOR</t>
+    <row r="1" ht="75" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>CHECKLIST APERTURA — PANADERÍA / OBRADOR</t>
         </is>
       </c>
     </row>
@@ -1914,7 +2199,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>TRAMITE</t>
+          <t>TRÁMITE</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1934,7 +2219,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1946,7 +2231,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Disenador</t>
+          <t>Diseñador</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -1956,12 +2241,12 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Estilo artesanal, rustico o moderno</t>
+          <t>Estilo artesanal, rústico o moderno</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -1983,12 +2268,12 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Categoria: Panaderia. Fotos pan recien hecho</t>
+          <t>Categoría: Panadería. Fotos pan recién hecho</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -2015,14 +2300,14 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Web basica</t>
+          <t>Web básica</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -2042,7 +2327,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -2054,7 +2339,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Fotografo</t>
+          <t>Fotógrafo</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -2069,7 +2354,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -2096,14 +2381,14 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Rotulacion</t>
+          <t>Rotulación</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -2119,14 +2404,14 @@
       <c r="E11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Inauguracion</t>
+          <t>Inauguración</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -2141,19 +2426,19 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Degustacion pan + cafe gratis</t>
+          <t>Degustación pan + café gratis</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Tarjeta fidelizacion</t>
+          <t>Tarjeta fidelización</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -2168,42 +2453,102 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>10a barra gratis</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="B15" s="8" t="inlineStr">
+          <t>La 10.ª barra, gratis</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Licencia de derechos de autor por la música ambiental (SGAE/AGEDI-AIE)</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>2 semanas</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>Dos licencias distintas y se pagan las dos, si pones música en la tienda</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>Cláusula informativa y consentimiento en la lista de correo y en los acuerdos con el canal mayorista</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Titular</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>Antes de abrir</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>WhatsApp, newsletter y los datos de contacto de restaurantes y hoteles del canal mayorista tratan datos: cada canal necesita su información previa</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C15">
-        <f>COUNTIF(A5:A13,"✓")</f>
+      <c r="C17" s="14">
+        <f>COUNTIF(A5:A15,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E15">
-        <f>COUNTIF(B5:B13,"?*")</f>
-        <v>9.0</v>
+      <c r="E17" s="14">
+        <f>COUNTIF(B5:B15,"?*")-COUNTIF(A5:A15,"N/A")</f>
+        <v>11.0</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:E13">
+  <conditionalFormatting sqref="A5:E15">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$A5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A5:A15">
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="1" stopIfTrue="1" text="✓">
+      <formula>NOT(ISERROR(SEARCH("✓",A5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
       <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2236,17 +2581,17 @@
     <col width="40" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>CHECKLIST APERTURA — PANADERIA / OBRADOR</t>
+    <row r="1" ht="75" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>CHECKLIST APERTURA — PANADERÍA / OBRADOR</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FASE 6: 90 DIAS</t>
+          <t>FASE 6: 90 DÍAS</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2604,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>TRAMITE</t>
+          <t>TRÁMITE</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -2279,14 +2624,14 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Control produccion diaria (kg)</t>
+          <t>Control producción diaria (kg)</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -2301,12 +2646,12 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Ajustar produccion a demanda real</t>
+          <t>Ajustar producción a demanda real</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -2333,7 +2678,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -2360,7 +2705,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -2382,19 +2727,19 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Potenciar lo que mas se vende</t>
+          <t>Potenciar lo que más se vende</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Optimizar horario produccion</t>
+          <t>Optimizar horario producción</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2414,14 +2759,14 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Resenas Google</t>
+          <t>Reseñas Google</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -2441,7 +2786,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -2468,7 +2813,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -2495,7 +2840,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
@@ -2522,14 +2867,14 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Evaluar 2o turno produccion</t>
+          <t>Evaluar un 2.º turno de producción</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -2544,7 +2889,7 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Si demanda crece: turno tarde para bolleria</t>
+          <t>Si demanda crece: turno tarde para bollería</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2900,7 @@
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C16">
+      <c r="C16" s="14">
         <f>COUNTIF(A5:A14,"✓")</f>
         <v>0.0</v>
       </c>
@@ -2564,12 +2909,13 @@
           <t>de</t>
         </is>
       </c>
-      <c r="E16">
-        <f>COUNTIF(B5:B14,"?*")</f>
+      <c r="E16" s="14">
+        <f>COUNTIF(B5:B14,"?*")-COUNTIF(A5:A14,"N/A")</f>
         <v>10.0</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
@@ -2578,8 +2924,13 @@
       <formula>$A5="✓"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A5:A14">
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="1" stopIfTrue="1" text="✓">
+      <formula>NOT(ISERROR(SEARCH("✓",A5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5 A6 A7 A8 A9 A10 A11 A12 A13 A14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, ☐, N/A. N/A = no aplica, sale del total." type="list">
       <formula1>"✓,☐,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2594,4 +2945,96 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="110" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>INSTRUCCIONES DE USO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Este fichero forma parte del producto «plan-negocio-panaderia» de AI Chef Pro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Las celdas VERDES son las editables: cambia esas y el resto del libro se recalcula solo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Columna OK: elige ✓ (hecho), ☐ (pendiente) o N/A (no aplica). Las N/A no cuentan en el total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>El contador de cada pestaña cuenta sólo las ✓; las N/A salen del total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Para editar una celda que no esté en verde: Revisar → Desproteger hoja (no tiene contraseña).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>Más plantillas y kits del catálogo en aichef.pro/productos-digitales</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>Versión 2.2 · septiembre 2026 · aichef.pro/plan-negocio-panaderia · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
 </file>